--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031253</v>
+        <v>122031254</v>
       </c>
       <c r="B2" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559946</v>
+        <v>559933</v>
       </c>
       <c r="R2" t="n">
         <v>6713650</v>
@@ -789,7 +789,7 @@
         <v>122031252</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031254</v>
+        <v>122031253</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559933</v>
+        <v>559946</v>
       </c>
       <c r="R4" t="n">
         <v>6713650</v>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031254</v>
+        <v>122031253</v>
       </c>
       <c r="B2" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559933</v>
+        <v>559946</v>
       </c>
       <c r="R2" t="n">
         <v>6713650</v>
@@ -789,7 +789,7 @@
         <v>122031252</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031253</v>
+        <v>122031254</v>
       </c>
       <c r="B4" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559946</v>
+        <v>559933</v>
       </c>
       <c r="R4" t="n">
         <v>6713650</v>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031253</v>
+        <v>122031252</v>
       </c>
       <c r="B2" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559946</v>
+        <v>560033</v>
       </c>
       <c r="R2" t="n">
         <v>6713650</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031252</v>
+        <v>122031253</v>
       </c>
       <c r="B3" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560033</v>
+        <v>559946</v>
       </c>
       <c r="R3" t="n">
         <v>6713650</v>
@@ -900,7 +900,7 @@
         <v>122031254</v>
       </c>
       <c r="B4" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031252</v>
+        <v>122031254</v>
       </c>
       <c r="B2" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560033</v>
+        <v>559933</v>
       </c>
       <c r="R2" t="n">
         <v>6713650</v>
@@ -789,7 +789,7 @@
         <v>122031253</v>
       </c>
       <c r="B3" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031254</v>
+        <v>122031252</v>
       </c>
       <c r="B4" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559933</v>
+        <v>560033</v>
       </c>
       <c r="R4" t="n">
         <v>6713650</v>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031254</v>
+        <v>122031253</v>
       </c>
       <c r="B2" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559933</v>
+        <v>559946</v>
       </c>
       <c r="R2" t="n">
         <v>6713650</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031253</v>
+        <v>122031252</v>
       </c>
       <c r="B3" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559946</v>
+        <v>560033</v>
       </c>
       <c r="R3" t="n">
         <v>6713650</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031252</v>
+        <v>122031254</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560033</v>
+        <v>559933</v>
       </c>
       <c r="R4" t="n">
         <v>6713650</v>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031253</v>
+        <v>122031254</v>
       </c>
       <c r="B2" t="n">
         <v>98159</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559946</v>
+        <v>559933</v>
       </c>
       <c r="R2" t="n">
         <v>6713650</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031254</v>
+        <v>122031253</v>
       </c>
       <c r="B4" t="n">
         <v>98159</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559933</v>
+        <v>559946</v>
       </c>
       <c r="R4" t="n">
         <v>6713650</v>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031253</v>
+        <v>122031254</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559946</v>
+        <v>559933</v>
       </c>
       <c r="R2" t="n">
         <v>6713650</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031254</v>
+        <v>122031252</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559933</v>
+        <v>560033</v>
       </c>
       <c r="R3" t="n">
         <v>6713650</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031252</v>
+        <v>122031253</v>
       </c>
       <c r="B4" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560033</v>
+        <v>559946</v>
       </c>
       <c r="R4" t="n">
         <v>6713650</v>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031252</v>
+        <v>122031253</v>
       </c>
       <c r="B3" t="n">
         <v>98185</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560033</v>
+        <v>559946</v>
       </c>
       <c r="R3" t="n">
         <v>6713650</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031253</v>
+        <v>122031252</v>
       </c>
       <c r="B4" t="n">
         <v>98185</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559946</v>
+        <v>560033</v>
       </c>
       <c r="R4" t="n">
         <v>6713650</v>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031254</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031253</v>
+        <v>122031252</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559946</v>
+        <v>560033</v>
       </c>
       <c r="R3" t="n">
         <v>6713650</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031252</v>
+        <v>122031253</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560033</v>
+        <v>559946</v>
       </c>
       <c r="R4" t="n">
         <v>6713650</v>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031254</v>
+        <v>122031252</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559933</v>
+        <v>560033</v>
       </c>
       <c r="R2" t="n">
         <v>6713650</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031252</v>
+        <v>122031253</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560033</v>
+        <v>559946</v>
       </c>
       <c r="R3" t="n">
         <v>6713650</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031253</v>
+        <v>122031254</v>
       </c>
       <c r="B4" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559946</v>
+        <v>559933</v>
       </c>
       <c r="R4" t="n">
         <v>6713650</v>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,6 +1006,333 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128241220</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98469</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vid Glasån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559918</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6713652</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128241219</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98469</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vid Glasån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>559940</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6713643</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flyttad 2025-09-04 till närliggande lokal, Artskyddsdispens Sveaskog, upddragsgivare TrV utförd av Jan henriksson, Amalina Natur och Miljökonsult och Janne Måreby, Nardus</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128241222</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98469</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vid Glasån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>559945</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6713657</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128241220</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128241219</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128241222</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128241220</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128241219</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128241222</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128241220</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128241219</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128241222</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128241220</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128241219</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128241222</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128241220</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128241219</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128241222</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128241220</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128241219</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128241222</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128241220</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128241219</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128241222</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128241220</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>128241219</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>128241222</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031252</v>
+        <v>128241272</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsken, Dlr</t>
+          <t>Vid Glasån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560033</v>
+        <v>560013</v>
       </c>
       <c r="R2" t="n">
-        <v>6713650</v>
+        <v>6713641</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jan Henriksson, Jan Måreby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031253</v>
+        <v>122031252</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +802,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,7 +811,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559946</v>
+        <v>560033</v>
       </c>
       <c r="R3" t="n">
         <v>6713650</v>
@@ -897,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122031254</v>
+        <v>122031253</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,7 +908,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,7 +917,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559933</v>
+        <v>559946</v>
       </c>
       <c r="R4" t="n">
         <v>6713650</v>
@@ -1008,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128241220</v>
+        <v>122031254</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,27 +1014,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vid Glasån, Dlr</t>
+          <t>Edsken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559918</v>
+        <v>559933</v>
       </c>
       <c r="R5" t="n">
-        <v>6713652</v>
+        <v>6713650</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,12 +1053,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,19 +1072,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Jan Måreby</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1121,7 +1093,7 @@
         <v>128241219</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128241222</v>
+        <v>128241220</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,24 +1231,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vid Glasån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559945</v>
+        <v>559918</v>
       </c>
       <c r="R7" t="n">
-        <v>6713657</v>
+        <v>6713652</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1317,6 +1292,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,6 +1308,227 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128241222</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vid Glasån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>559945</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6713657</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128241223</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vid Glasån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>560035</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6713645</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Dessa plantor har 2025-09-15/16 flyttats som en del i en Artskyddsdispens. Den nya växtplatsen ligger i en nyckelbiotop strax söder om. De utplanterade knärötternas växtplats har rapporterats till ArtP</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Henriksson, Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60017-2024 artfynd.xlsx
+++ b/artfynd/A 60017-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128241272</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031252</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031253</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031254</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128241219</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128241220</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128241222</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,8 +1569,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128241223</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>